--- a/output/pdf_financials_xlsx/APGO.xlsx
+++ b/output/pdf_financials_xlsx/APGO.xlsx
@@ -1358,10 +1358,10 @@
         <v>4.145914</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2.99387</v>
+        <v>-2.99387</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>9.381345</v>
+        <v>-9.381345</v>
       </c>
     </row>
     <row r="17">
@@ -1411,13 +1411,13 @@
         <v>-0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.421708</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-22.041486</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-8.291828000000001</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-0</v>
@@ -1657,19 +1657,19 @@
         <v>-0.13635</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.710854</v>
+        <v>-2.710854</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>11.020743</v>
+        <v>-11.020743</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>4.145914</v>
+        <v>-4.145914</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.99387</v>
+        <v>-2.99387</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>9.381345</v>
+        <v>-9.381345</v>
       </c>
     </row>
     <row r="21">
@@ -1843,19 +1843,19 @@
         <v>-0.13635</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.710854</v>
+        <v>-2.710854</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>11.020743</v>
+        <v>-11.020743</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>4.145914</v>
+        <v>-4.145914</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.99387</v>
+        <v>-2.99387</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>9.381345</v>
+        <v>-9.381345</v>
       </c>
     </row>
     <row r="24">
@@ -2045,16 +2045,16 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>90.3618</v>
+        <v>-90.3618</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>183.67905</v>
+        <v>-183.67905</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>207.2957</v>
+        <v>-207.2957</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>149.6935</v>
+        <v>-149.6935</v>
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
         <v>4.145914</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.99387</v>
+        <v>-2.99387</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>9.381345</v>
+        <v>-9.381345</v>
       </c>
     </row>
     <row r="28">
@@ -2242,10 +2242,10 @@
         <v>4.284898</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.133102</v>
+        <v>-2.854638</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>9.52521</v>
+        <v>-9.23748</v>
       </c>
     </row>
     <row r="30">
@@ -2387,19 +2387,19 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6268,31 +6268,31 @@
         <v>0.6236660000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.631487</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.631487</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.671372</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.672095</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.672095</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.672095</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.672095</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.672095</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.442352</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.774936</v>
+        <v>-0.648264</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-0.896431</v>
@@ -11469,7 +11469,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12835,7 +12839,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -13429,7 +13437,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13940,7 +13952,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14550,7 +14566,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -15855,7 +15875,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -34239,7 +34263,11 @@
           <t>Recovery of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -37531,19 +37559,19 @@
         </is>
       </c>
       <c r="Q286" s="5" t="n">
-        <v>2.710854</v>
+        <v>-2.710854</v>
       </c>
       <c r="R286" s="5" t="n">
-        <v>11.020743</v>
+        <v>-11.020743</v>
       </c>
       <c r="S286" s="5" t="n">
-        <v>4.145914</v>
+        <v>-4.145914</v>
       </c>
       <c r="T286" s="5" t="n">
-        <v>2.99387</v>
+        <v>-2.99387</v>
       </c>
       <c r="U286" s="5" t="n">
-        <v>9.381345</v>
+        <v>-9.381345</v>
       </c>
     </row>
     <row r="287">
@@ -37820,19 +37848,19 @@
         </is>
       </c>
       <c r="Q289" s="5" t="n">
-        <v>1.171917</v>
+        <v>-1.171917</v>
       </c>
       <c r="R289" s="5" t="n">
-        <v>11.12543</v>
+        <v>-11.12543</v>
       </c>
       <c r="S289" s="5" t="n">
-        <v>4.150369</v>
+        <v>-4.150369</v>
       </c>
       <c r="T289" s="5" t="n">
-        <v>2.988538</v>
+        <v>-2.988538</v>
       </c>
       <c r="U289" s="5" t="n">
-        <v>9.398012</v>
+        <v>-9.398012</v>
       </c>
     </row>
     <row r="290">

--- a/output/pdf_financials_xlsx/APGO.xlsx
+++ b/output/pdf_financials_xlsx/APGO.xlsx
@@ -2518,34 +2518,34 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.119215</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.01978</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.054912</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.013841</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.170082</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.038098</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.058486</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.008902</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.059471</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.010822</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>15.746122</v>
@@ -2642,34 +2642,34 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.119215</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.01978</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.054912</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.017841</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.170082</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.038098</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.058486</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.008902</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.059471</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.010822</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>15.746122</v>
@@ -3386,34 +3386,34 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.119215</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.03235</v>
+        <v>0.01257</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.104093</v>
+        <v>0.049181</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.013841</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.170082</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.038098</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.06848600000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.018902</v>
+        <v>0.01</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.069471</v>
+        <v>0.01</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.020822</v>
+        <v>0.01</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1.068144</v>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/output/pdf_financials_xlsx/APGO.xlsx
+++ b/output/pdf_financials_xlsx/APGO.xlsx
@@ -764,7 +764,7 @@
         <v>0.117893</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.390783</v>
+        <v>0.395783</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.528911</v>
@@ -773,13 +773,13 @@
         <v>0.197222</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.16543</v>
+        <v>0.18043</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.156374</v>
+        <v>0.172374</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.108527</v>
+        <v>0.110927</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.107818</v>
@@ -950,7 +950,7 @@
         <v>0.117893</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.390783</v>
+        <v>0.395783</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.528911</v>
@@ -959,13 +959,13 @@
         <v>0.197222</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.16543</v>
+        <v>0.18043</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.156374</v>
+        <v>0.172374</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.108527</v>
+        <v>0.110927</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.107818</v>
@@ -1012,7 +1012,7 @@
         <v>-0.117893</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.390783</v>
+        <v>-0.395783</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.528911</v>
@@ -1021,13 +1021,13 @@
         <v>-0.197222</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.16543</v>
+        <v>-0.18043</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.156374</v>
+        <v>-0.172374</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.108527</v>
+        <v>-0.110927</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.107818</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.084425</v>
+        <v>-0.195049</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.997</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.8893760000000001</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -6799,16 +6799,16 @@
         <v>-0.003762</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.002029</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.00168</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006117</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.005274</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>-0.031734</v>
@@ -7109,16 +7109,16 @@
         <v>0.06454</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.040207</v>
+        <v>-0.038178</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.020045</v>
+        <v>0.021725</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.023025</v>
+        <v>0.016908</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.081108</v>
+        <v>0.086382</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>-1.587047</v>
@@ -7431,19 +7431,19 @@
         <v>-0.001443</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.050757</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.165482</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003643</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0091</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015756</v>
       </c>
     </row>
     <row r="112">
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.006515</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -8891,19 +8891,19 @@
         <v>-0.001443</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.050757</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.165482</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003643</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0091</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015756</v>
       </c>
     </row>
     <row r="135">
@@ -8953,19 +8953,19 @@
         <v>-0.048649</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-4.100056</v>
+        <v>-4.150813</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-9.121041999999999</v>
+        <v>-9.286524</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-5.683303</v>
+        <v>-5.686946</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-2.867956</v>
+        <v>-2.877056</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-8.806787999999999</v>
+        <v>-8.822544000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17431,7 +17431,11 @@
           <t>Acquisition of equipment 8</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -24867,7 +24871,11 @@
           <t>Acquisition of equipment 7</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -27475,7 +27483,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -31431,7 +31443,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -40999,7 +41015,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -42399,7 +42419,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -42805,7 +42829,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -43617,7 +43645,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -43716,7 +43748,11 @@
           <t>Loss from discontinued operations (Note 3)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
